--- a/inst/extdata/projects/Example/Configurations/Scenarios.xlsx
+++ b/inst/extdata/projects/Example/Configurations/Scenarios.xlsx
@@ -1,55 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -68,99 +54,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Pavel Balazki</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Pavel Balazki:
-Simulation time is defined as time intervals.
-Expected is a triple of values {start, end, resolution}, resolution given in "points per &lt;time unit&gt;" as defined in the columne "SimulationTimeUnit". Multiple intervals can be separated by a ";"</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -174,44 +78,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -238,15 +142,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -273,7 +176,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -285,170 +187,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23.140625" customWidth="1" min="1" max="1"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="14.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="23.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="22.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="18.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.140625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="16.140625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="20.140625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="30" bestFit="1" customWidth="1" min="13" max="13"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario_name</t>
@@ -504,7 +411,7 @@
           <t>SteadyStateTimeUnit</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>OverwriteFormulasInSS</t>
         </is>
@@ -523,17 +430,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TestScenario</t>
+          <t>Aciclovir_iv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Indiv1</t>
-        </is>
+          <t>Adult_male</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global, Aciclovir</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -550,6 +460,20 @@
         <is>
           <t>h</t>
         </is>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -560,17 +484,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TestScenario2</t>
+          <t>Aciclovir_iv_female</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indiv1</t>
-        </is>
+          <t>Adult_female</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>"Global", "Aciclovir", "Sheet, with comma"</t>
+          <t>Global, Aciclovir</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,7 +507,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0, 1, 60; 1, 12, 20</t>
+          <t>0, 24, 60</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -589,41 +516,39 @@
         </is>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>500</v>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Aciclovir_PVB, Aciclovir_fat_cell</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PopulationScenario</t>
+          <t>Aciclovir_iv_population</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indiv1</t>
+          <t>Adult_male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TestPopulation</t>
+          <t>European_adults</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -631,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global, Aciclovir</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -641,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0, 12, 20</t>
+          <t>0, 24, 60</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -652,92 +577,18 @@
       <c r="I4" t="b">
         <v>0</v>
       </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>Aciclovir.pkml</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PopulationScenarioFromCSV</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Indiv1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TestPopulation</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Aciclovir_iv_250mg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0, 12, 20</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Aciclovir.pkml</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TestScenario_missingParam</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Indiv1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Global, MissingParam</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Aciclovir_iv_250mg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0, 24, 60</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
@@ -745,25 +596,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OutputPathId</t>
@@ -801,6 +642,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>